--- a/01_analyses_states/Mizoram/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Mizoram/results/SoIB_summaries.xlsx
@@ -569,10 +569,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C8">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -667,7 +667,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -675,7 +675,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -683,7 +683,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +712,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -777,13 +777,13 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2">
-        <v>93.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>97.09999999999999</v>
@@ -797,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="D3">
         <v>3</v>
